--- a/src/nodes/P/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/P/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0.00044694783742893994</v>
+        <v>0.00034638457400742854</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.004138405902119815</v>
       </c>
       <c r="B2">
-        <v>0.0013542204009512062</v>
+        <v>0.0011511821848911444</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.00827681180423963</v>
       </c>
       <c r="B3">
-        <v>0.0021912796857401456</v>
+        <v>0.0018962941130370456</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.012415217706359446</v>
       </c>
       <c r="B4">
-        <v>0.0029776397676569786</v>
+        <v>0.0025968523710754874</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.01655362360847926</v>
       </c>
       <c r="B5">
-        <v>0.0037328147225629219</v>
+        <v>0.0032679889716368247</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.020692029510599074</v>
       </c>
       <c r="B6">
-        <v>0.0044680154741554385</v>
+        <v>0.0039184007568329824</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.024830435412718892</v>
       </c>
       <c r="B7">
-        <v>0.0051612403374769631</v>
+        <v>0.0045310438867021581</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.028968841314838706</v>
       </c>
       <c r="B8">
-        <v>0.00578932058337779</v>
+        <v>0.0050879697225206912</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.03310724721695852</v>
       </c>
       <c r="B9">
-        <v>0.0063576319145947028</v>
+        <v>0.0055933511125912157</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.037245653119078334</v>
       </c>
       <c r="B10">
-        <v>0.0068766717271896783</v>
+        <v>0.0060553298285724805</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.041384059021198148</v>
       </c>
       <c r="B11">
-        <v>0.0073488797586390032</v>
+        <v>0.0064758018485213875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.045522464923317969</v>
       </c>
       <c r="B12">
-        <v>0.007774681331772536</v>
+        <v>0.0068551017020943876</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.049660870825437783</v>
       </c>
       <c r="B13">
-        <v>0.0081545017694201419</v>
+        <v>0.00719356391894792</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0537992767275576</v>
       </c>
       <c r="B14">
-        <v>0.0084887921663179041</v>
+        <v>0.0074915426650391647</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.057937682629677412</v>
       </c>
       <c r="B15">
-        <v>0.008778106704826821</v>
+        <v>0.0077494706515282381</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.062076088531797219</v>
       </c>
       <c r="B16">
-        <v>0.00902302533921411</v>
+        <v>0.0079678002258759834</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.06621449443391704</v>
       </c>
       <c r="B17">
-        <v>0.0092241280237469955</v>
+        <v>0.00814698373554325</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.070352900336036861</v>
       </c>
       <c r="B18">
-        <v>0.0093817638027034484</v>
+        <v>0.00828729425360292</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.074491306238156668</v>
       </c>
       <c r="B19">
-        <v>0.009495358080404465</v>
+        <v>0.0083882877555760283</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.078629712140276489</v>
       </c>
       <c r="B20">
-        <v>0.00956410535118179</v>
+        <v>0.0084493409425956418</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.0827681180423963</v>
       </c>
       <c r="B21">
-        <v>0.0095872001093671791</v>
+        <v>0.00846983051579483</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.086906523944516118</v>
       </c>
       <c r="B22">
-        <v>0.00956410535118179</v>
+        <v>0.0084493409425956418</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.091044929846635939</v>
       </c>
       <c r="B23">
-        <v>0.009495358080404465</v>
+        <v>0.0083882877555760283</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.095183335748755746</v>
       </c>
       <c r="B24">
-        <v>0.0093817638027034484</v>
+        <v>0.00828729425360292</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.099321741650875567</v>
       </c>
       <c r="B25">
-        <v>0.0092241280237469938</v>
+        <v>0.0081469837355432478</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.10346014755299537</v>
       </c>
       <c r="B26">
-        <v>0.00902302533921411</v>
+        <v>0.0079678002258759834</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.1075985534551152</v>
       </c>
       <c r="B27">
-        <v>0.00877810670482682</v>
+        <v>0.0077494706515282372</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.111736959357235</v>
       </c>
       <c r="B28">
-        <v>0.0084887921663179024</v>
+        <v>0.0074915426650391638</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.11587536525935482</v>
       </c>
       <c r="B29">
-        <v>0.00815450176942014</v>
+        <v>0.0071935639189479178</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.12001377116147464</v>
       </c>
       <c r="B30">
-        <v>0.0077746813317725351</v>
+        <v>0.006855101702094385</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.12415217706359444</v>
       </c>
       <c r="B31">
-        <v>0.0073488797586390032</v>
+        <v>0.0064758018485213892</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.12829058296571427</v>
       </c>
       <c r="B32">
-        <v>0.0068766717271896791</v>
+        <v>0.0060553298285724805</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.13242898886783408</v>
       </c>
       <c r="B33">
-        <v>0.0063576319145947028</v>
+        <v>0.0055933511125912157</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.13656739476995389</v>
       </c>
       <c r="B34">
-        <v>0.0057893205833777894</v>
+        <v>0.0050879697225206895</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.14070580067207372</v>
       </c>
       <c r="B35">
-        <v>0.00516124033747696</v>
+        <v>0.0045310438867021546</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.14484420657419353</v>
       </c>
       <c r="B36">
-        <v>0.0044680154741554385</v>
+        <v>0.0039184007568329824</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.14898261247631334</v>
       </c>
       <c r="B37">
-        <v>0.0037328147225629219</v>
+        <v>0.0032679889716368247</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.15312101837843314</v>
       </c>
       <c r="B38">
-        <v>0.0029776397676569769</v>
+        <v>0.0025968523710754861</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.15725942428055298</v>
       </c>
       <c r="B39">
-        <v>0.0021912796857401422</v>
+        <v>0.0018962941130370424</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.16139783018267279</v>
       </c>
       <c r="B40">
-        <v>0.0013542204009512012</v>
+        <v>0.00115118218489114</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.16553623608479259</v>
       </c>
       <c r="B41">
-        <v>0.00044694783742893989</v>
+        <v>0.00034638457400742859</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.16553623608479259</v>
       </c>
       <c r="B42">
-        <v>-0.00044694783742893994</v>
+        <v>-0.00034638457400742854</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.16139783018267279</v>
       </c>
       <c r="B43">
-        <v>-0.00045056374180489726</v>
+        <v>-0.0002475255257448363</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.15725942428055298</v>
       </c>
       <c r="B44">
-        <v>-0.000430814293842969</v>
+        <v>-0.00013582872113986918</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.15312101837843314</v>
       </c>
       <c r="B45">
-        <v>-0.00040713709084516642</v>
+        <v>-2.6349694263675522E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.14898261247631334</v>
       </c>
       <c r="B46">
-        <v>-0.00039896973011350069</v>
+        <v>6.5856020812596561E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.14484420657419353</v>
       </c>
       <c r="B47">
-        <v>-0.00041744867982195747</v>
+        <v>0.00013216603750049928</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.14070580067207372</v>
       </c>
       <c r="B48">
-        <v>-0.00044050589163241905</v>
+        <v>0.00018969055914238564</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.13656739476995389</v>
       </c>
       <c r="B49">
-        <v>-0.00044490929090754236</v>
+        <v>0.00025644156994955684</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.13242898886783408</v>
       </c>
       <c r="B50">
-        <v>-0.00043597521432518467</v>
+        <v>0.00032830558767830205</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.12829058296571427</v>
       </c>
       <c r="B51">
-        <v>-0.00042414514940764507</v>
+        <v>0.00039719674920955333</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.12415217706359444</v>
       </c>
       <c r="B52">
-        <v>-0.00041181277573978925</v>
+        <v>0.00046126513437782433</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.12001377116147464</v>
       </c>
       <c r="B53">
-        <v>-0.0003993598209221245</v>
+        <v>0.00052021980875602422</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.11587536525935482</v>
       </c>
       <c r="B54">
-        <v>-0.00038716801255515789</v>
+        <v>0.00057376983791706257</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.111736959357235</v>
       </c>
       <c r="B55">
-        <v>-0.00037564784504866213</v>
+        <v>0.000621601656230076</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.1075985534551152</v>
       </c>
       <c r="B56">
-        <v>-0.00036532488004947192</v>
+        <v>0.00066331117324911024</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.10346014755299537</v>
       </c>
       <c r="B57">
-        <v>-0.00035675344601368732</v>
+        <v>0.00069847166732443918</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.099321741650875567</v>
       </c>
       <c r="B58">
-        <v>-0.00035048787139740841</v>
+        <v>0.00072665641680633608</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.095183335748755746</v>
       </c>
       <c r="B59">
-        <v>-0.0003468544115234701</v>
+        <v>0.00074761513757705736</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.091044929846635939</v>
       </c>
       <c r="B60">
-        <v>-0.00034526702918164621</v>
+        <v>0.00076180329564679049</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.086906523944516118</v>
       </c>
       <c r="B61">
-        <v>-0.00034491161402844554</v>
+        <v>0.00076985279455770545</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.0827681180423963</v>
       </c>
       <c r="B62">
-        <v>-0.00034497405572037667</v>
+        <v>0.00077239553785197264</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.078629712140276489</v>
       </c>
       <c r="B63">
-        <v>-0.00034491161402844554</v>
+        <v>0.00076985279455770545</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.074491306238156668</v>
       </c>
       <c r="B64">
-        <v>-0.00034526702918164621</v>
+        <v>0.00076180329564679049</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.070352900336036861</v>
       </c>
       <c r="B65">
-        <v>-0.0003468544115234701</v>
+        <v>0.00074761513757705747</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.06621449443391704</v>
       </c>
       <c r="B66">
-        <v>-0.00035048787139740841</v>
+        <v>0.00072665641680633619</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.062076088531797219</v>
       </c>
       <c r="B67">
-        <v>-0.00035675344601368732</v>
+        <v>0.00069847166732443929</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.057937682629677412</v>
       </c>
       <c r="B68">
-        <v>-0.00036532488004947187</v>
+        <v>0.00066331117324911057</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0537992767275576</v>
       </c>
       <c r="B69">
-        <v>-0.00037564784504866207</v>
+        <v>0.00062160165623007619</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.049660870825437783</v>
       </c>
       <c r="B70">
-        <v>-0.00038716801255515778</v>
+        <v>0.000573769837917063</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.045522464923317969</v>
       </c>
       <c r="B71">
-        <v>-0.00039935982092212445</v>
+        <v>0.00052021980875602443</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.041384059021198148</v>
       </c>
       <c r="B72">
-        <v>-0.00041181277573978925</v>
+        <v>0.00046126513437782423</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.037245653119078334</v>
       </c>
       <c r="B73">
-        <v>-0.00042414514940764507</v>
+        <v>0.00039719674920955323</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.03310724721695852</v>
       </c>
       <c r="B74">
-        <v>-0.00043597521432518467</v>
+        <v>0.00032830558767830205</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.028968841314838706</v>
       </c>
       <c r="B75">
-        <v>-0.00044490929090754242</v>
+        <v>0.00025644156994955705</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.024830435412718892</v>
       </c>
       <c r="B76">
-        <v>-0.00044050589163241915</v>
+        <v>0.000189690559142386</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.020692029510599074</v>
       </c>
       <c r="B77">
-        <v>-0.00041744867982195747</v>
+        <v>0.00013216603750049928</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.01655362360847926</v>
       </c>
       <c r="B78">
-        <v>-0.00039896973011350069</v>
+        <v>6.5856020812596561E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.012415217706359446</v>
       </c>
       <c r="B79">
-        <v>-0.00040713709084516631</v>
+        <v>-2.6349694263675254E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.00827681180423963</v>
       </c>
       <c r="B80">
-        <v>-0.00043081429384296885</v>
+        <v>-0.00013582872113986866</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.004138405902119815</v>
       </c>
       <c r="B81">
-        <v>-0.00045056374180489715</v>
+        <v>-0.0002475255257448357</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-0.00044694783742893994</v>
+        <v>-0.00034638457400742854</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0.00024659585419893181</v>
+        <v>0.00016439723613262123</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0045665898925728128</v>
       </c>
       <c r="B2">
-        <v>0.00056692613886487613</v>
+        <v>0.00040096632205948785</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0091331797851456255</v>
       </c>
       <c r="B3">
-        <v>0.000857899616808902</v>
+        <v>0.00061678367048105759</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.013699769677718441</v>
       </c>
       <c r="B4">
-        <v>0.0011302618604587631</v>
+        <v>0.00081901303349029252</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.018266359570291251</v>
       </c>
       <c r="B5">
-        <v>0.001394758442242213</v>
+        <v>0.0010148181631801552</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.022832949462864065</v>
       </c>
       <c r="B6">
-        <v>0.001657554367094998</v>
+        <v>0.0012083090990347336</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.027399539355436882</v>
       </c>
       <c r="B7">
-        <v>0.0019064923699848345</v>
+        <v>0.0013913810301026213</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.031966129248009692</v>
       </c>
       <c r="B8">
-        <v>0.0021287721174103242</v>
+        <v>0.0015555004317010974</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0365327191405825</v>
       </c>
       <c r="B9">
-        <v>0.00232734327196164</v>
+        <v>0.001702633774657679</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.041099309033155319</v>
       </c>
       <c r="B10">
-        <v>0.002507982252095265</v>
+        <v>0.0018366320320520693</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.045665898925728129</v>
       </c>
       <c r="B11">
-        <v>0.0026720225036413526</v>
+        <v>0.001958384190462477</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.050232488818300947</v>
       </c>
       <c r="B12">
-        <v>0.0028196867292734746</v>
+        <v>0.0020680387398417351</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.054799078710873764</v>
       </c>
       <c r="B13">
-        <v>0.0029511976316652019</v>
+        <v>0.0021657441701426789</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.059365668603446567</v>
       </c>
       <c r="B14">
-        <v>0.0030667929544963713</v>
+        <v>0.0022516589971899002</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.063932258496019384</v>
       </c>
       <c r="B15">
-        <v>0.0031667706054718807</v>
+        <v>0.0023259818402950275</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.068498848388592187</v>
       </c>
       <c r="B16">
-        <v>0.0032514435333028959</v>
+        <v>0.002388921344641446</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.073065438281165</v>
       </c>
       <c r="B17">
-        <v>0.0033211246867005805</v>
+        <v>0.0024406861554125427</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.077632028173737822</v>
       </c>
       <c r="B18">
-        <v>0.0033760003921007088</v>
+        <v>0.0024814005015359273</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.082198618066310639</v>
       </c>
       <c r="B19">
-        <v>0.0034157504868374943</v>
+        <v>0.0025108509469161065</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.086765207958883456</v>
       </c>
       <c r="B20">
-        <v>0.0034399281859697622</v>
+        <v>0.0025287396392018116</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.091331797851456259</v>
       </c>
       <c r="B21">
-        <v>0.0034480867045563351</v>
+        <v>0.0025347687260417729</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.095898387744029076</v>
       </c>
       <c r="B22">
-        <v>0.0034399281859697622</v>
+        <v>0.0025287396392018116</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.10046497763660189</v>
       </c>
       <c r="B23">
-        <v>0.0034157504868374943</v>
+        <v>0.0025108509469161065</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.10503156752917471</v>
       </c>
       <c r="B24">
-        <v>0.0033760003921007088</v>
+        <v>0.0024814005015359273</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.10959815742174753</v>
       </c>
       <c r="B25">
-        <v>0.0033211246867005805</v>
+        <v>0.0024406861554125423</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.11416474731432033</v>
       </c>
       <c r="B26">
-        <v>0.0032514435333028959</v>
+        <v>0.002388921344641446</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.11873133720689313</v>
       </c>
       <c r="B27">
-        <v>0.0031667706054718807</v>
+        <v>0.0023259818402950271</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.12329792709946595</v>
       </c>
       <c r="B28">
-        <v>0.0030667929544963704</v>
+        <v>0.0022516589971899</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.12786451699203877</v>
       </c>
       <c r="B29">
-        <v>0.0029511976316652011</v>
+        <v>0.0021657441701426784</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.1324311068846116</v>
       </c>
       <c r="B30">
-        <v>0.0028196867292734741</v>
+        <v>0.0020680387398417347</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.13699769677718438</v>
       </c>
       <c r="B31">
-        <v>0.002672022503641353</v>
+        <v>0.001958384190462477</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.14156428666975721</v>
       </c>
       <c r="B32">
-        <v>0.002507982252095265</v>
+        <v>0.0018366320320520697</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.14613087656233</v>
       </c>
       <c r="B33">
-        <v>0.00232734327196164</v>
+        <v>0.001702633774657679</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.15069746645490284</v>
       </c>
       <c r="B34">
-        <v>0.0021287721174103233</v>
+        <v>0.0015555004317010968</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.15526405634747564</v>
       </c>
       <c r="B35">
-        <v>0.0019064923699848332</v>
+        <v>0.0013913810301026204</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.15983064624004845</v>
       </c>
       <c r="B36">
-        <v>0.001657554367094998</v>
+        <v>0.0012083090990347336</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.16439723613262128</v>
       </c>
       <c r="B37">
-        <v>0.001394758442242213</v>
+        <v>0.0010148181631801552</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.16896382602519408</v>
       </c>
       <c r="B38">
-        <v>0.0011302618604587626</v>
+        <v>0.00081901303349029219</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.17353041591776691</v>
       </c>
       <c r="B39">
-        <v>0.0008578996168089008</v>
+        <v>0.00061678367048105661</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.17809700581033972</v>
       </c>
       <c r="B40">
-        <v>0.00056692613886487439</v>
+        <v>0.00040096632205948655</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.18266359570291252</v>
       </c>
       <c r="B41">
-        <v>0.00024659585419893181</v>
+        <v>0.00016439723613262132</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.18266359570291252</v>
       </c>
       <c r="B42">
-        <v>-0.00024659585419893181</v>
+        <v>-0.00016439723613262123</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.17809700581033972</v>
       </c>
       <c r="B43">
-        <v>-0.00042883276196745281</v>
+        <v>-0.00026287294516206503</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.17353041591776691</v>
       </c>
       <c r="B44">
-        <v>-0.00058879606115816408</v>
+        <v>-0.00034768011483032</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.16896382602519408</v>
       </c>
       <c r="B45">
-        <v>-0.00073723110135205975</v>
+        <v>-0.0004259822743835893</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.16439723613262128</v>
       </c>
       <c r="B46">
-        <v>-0.0008848832321301346</v>
+        <v>-0.00050494295306807669</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.15983064624004845</v>
       </c>
       <c r="B47">
-        <v>-0.0010379172412665889</v>
+        <v>-0.00058867197320632459</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.15526405634747564</v>
       </c>
       <c r="B48">
-        <v>-0.0011841756693084446</v>
+        <v>-0.00066906432942623177</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.15069746645490284</v>
       </c>
       <c r="B49">
-        <v>-0.0013108579968450363</v>
+        <v>-0.00073758631113581</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.14613087656233</v>
       </c>
       <c r="B50">
-        <v>-0.0014209137118621246</v>
+        <v>-0.000796204214558164</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.14156428666975721</v>
       </c>
       <c r="B51">
-        <v>-0.0015201190681639067</v>
+        <v>-0.00084876884812071175</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.13699769677718438</v>
       </c>
       <c r="B52">
-        <v>-0.0016098073754319032</v>
+        <v>-0.00089616906225302743</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.1324311068846116</v>
       </c>
       <c r="B53">
-        <v>-0.0016902012073169638</v>
+        <v>-0.00093855321788522425</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.12786451699203877</v>
       </c>
       <c r="B54">
-        <v>-0.0017615231374699394</v>
+        <v>-0.000976069675947416</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.12329792709946595</v>
       </c>
       <c r="B55">
-        <v>-0.0018240107893424556</v>
+        <v>-0.0010088768320359847</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.11873133720689313</v>
       </c>
       <c r="B56">
-        <v>-0.0018779619855892422</v>
+        <v>-0.0010371732204123886</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.11416474731432033</v>
       </c>
       <c r="B57">
-        <v>-0.0019236895986658046</v>
+        <v>-0.0010611674100043545</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.10959815742174753</v>
       </c>
       <c r="B58">
-        <v>-0.0019615065010276478</v>
+        <v>-0.0010810679697396096</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.10503156752917471</v>
       </c>
       <c r="B59">
-        <v>-0.0019915989512879818</v>
+        <v>-0.0010969990607232003</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.10046497763660189</v>
       </c>
       <c r="B60">
-        <v>-0.0020136467526908359</v>
+        <v>-0.0011087472127694477</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.095898387744029076</v>
       </c>
       <c r="B61">
-        <v>-0.0020272030946379437</v>
+        <v>-0.0011160145478699931</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.091331797851456259</v>
       </c>
       <c r="B62">
-        <v>-0.002031821166531039</v>
+        <v>-0.0011185031880164768</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.086765207958883456</v>
       </c>
       <c r="B63">
-        <v>-0.0020272030946379437</v>
+        <v>-0.0011160145478699931</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.082198618066310639</v>
       </c>
       <c r="B64">
-        <v>-0.0020136467526908359</v>
+        <v>-0.0011087472127694477</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.077632028173737822</v>
       </c>
       <c r="B65">
-        <v>-0.0019915989512879822</v>
+        <v>-0.0010969990607232003</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.073065438281165</v>
       </c>
       <c r="B66">
-        <v>-0.0019615065010276478</v>
+        <v>-0.0010810679697396098</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.068498848388592187</v>
       </c>
       <c r="B67">
-        <v>-0.0019236895986658046</v>
+        <v>-0.0010611674100043545</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.063932258496019384</v>
       </c>
       <c r="B68">
-        <v>-0.0018779619855892424</v>
+        <v>-0.0010371732204123886</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.059365668603446567</v>
       </c>
       <c r="B69">
-        <v>-0.0018240107893424558</v>
+        <v>-0.001008876832035985</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.054799078710873764</v>
       </c>
       <c r="B70">
-        <v>-0.0017615231374699396</v>
+        <v>-0.00097606967594741619</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.050232488818300947</v>
       </c>
       <c r="B71">
-        <v>-0.0016902012073169643</v>
+        <v>-0.00093855321788522458</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.045665898925728129</v>
       </c>
       <c r="B72">
-        <v>-0.0016098073754319032</v>
+        <v>-0.00089616906225302732</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.041099309033155319</v>
       </c>
       <c r="B73">
-        <v>-0.0015201190681639067</v>
+        <v>-0.00084876884812071164</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0365327191405825</v>
       </c>
       <c r="B74">
-        <v>-0.0014209137118621246</v>
+        <v>-0.000796204214558164</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.031966129248009692</v>
       </c>
       <c r="B75">
-        <v>-0.0013108579968450368</v>
+        <v>-0.00073758631113581008</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.027399539355436882</v>
       </c>
       <c r="B76">
-        <v>-0.0011841756693084452</v>
+        <v>-0.0006690643294262322</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.022832949462864065</v>
       </c>
       <c r="B77">
-        <v>-0.0010379172412665889</v>
+        <v>-0.00058867197320632459</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.018266359570291251</v>
       </c>
       <c r="B78">
-        <v>-0.0008848832321301346</v>
+        <v>-0.00050494295306807669</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.013699769677718441</v>
       </c>
       <c r="B79">
-        <v>-0.00073723110135206</v>
+        <v>-0.00042598227438358946</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0091331797851456255</v>
       </c>
       <c r="B80">
-        <v>-0.00058879606115816484</v>
+        <v>-0.00034768011483032033</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0045665898925728128</v>
       </c>
       <c r="B81">
-        <v>-0.00042883276196745379</v>
+        <v>-0.00026287294516206557</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-0.00024659585419893181</v>
+        <v>-0.00016439723613262123</v>
       </c>
     </row>
   </sheetData>
